--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0001T0006Z000C1N4_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0001T0006Z000C1N4_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>61.22963608956841</v>
+        <v>9.949815864554866</v>
       </c>
       <c r="D2" t="n">
-        <v>58.64028072532236</v>
+        <v>9.529045617864885</v>
       </c>
       <c r="E2" t="n">
-        <v>16.06448901065523</v>
+        <v>2.610479464231475</v>
       </c>
       <c r="F2" t="n">
-        <v>16.01887623980861</v>
+        <v>2.6030673889689</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>58.14281611310363</v>
+        <v>9.448207618379341</v>
       </c>
       <c r="D3" t="n">
-        <v>55.96102158706976</v>
+        <v>9.093666007898836</v>
       </c>
       <c r="E3" t="n">
-        <v>16.06448901065523</v>
+        <v>2.610479464231475</v>
       </c>
       <c r="F3" t="n">
-        <v>16.01887623980861</v>
+        <v>2.6030673889689</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>37.77013235251774</v>
+        <v>6.137646507284133</v>
       </c>
       <c r="D4" t="n">
-        <v>36.34419647442471</v>
+        <v>5.905931927094016</v>
       </c>
       <c r="E4" t="n">
-        <v>16.06448901065523</v>
+        <v>2.610479464231475</v>
       </c>
       <c r="F4" t="n">
-        <v>16.01887623980861</v>
+        <v>2.6030673889689</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>38.70003625610562</v>
+        <v>6.288755891617163</v>
       </c>
       <c r="D5" t="n">
-        <v>36.7121272251328</v>
+        <v>5.965720674084079</v>
       </c>
       <c r="E5" t="n">
-        <v>16.06448901065523</v>
+        <v>2.610479464231475</v>
       </c>
       <c r="F5" t="n">
-        <v>16.01887623980861</v>
+        <v>2.6030673889689</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>46.40386444307818</v>
+        <v>7.540627972000204</v>
       </c>
       <c r="D6" t="n">
-        <v>44.95577577966763</v>
+        <v>7.305313564195989</v>
       </c>
       <c r="E6" t="n">
-        <v>16.06448901065523</v>
+        <v>2.610479464231475</v>
       </c>
       <c r="F6" t="n">
-        <v>16.01887623980861</v>
+        <v>2.6030673889689</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>40.49471890497837</v>
+        <v>6.580391822058985</v>
       </c>
       <c r="D7" t="n">
-        <v>39.86412893388332</v>
+        <v>6.47792095175604</v>
       </c>
       <c r="E7" t="n">
-        <v>16.06448901065523</v>
+        <v>2.610479464231475</v>
       </c>
       <c r="F7" t="n">
-        <v>16.01887623980861</v>
+        <v>2.6030673889689</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>16.19027036163108</v>
+        <v>2.63091893376505</v>
       </c>
       <c r="D8" t="n">
-        <v>15.5430831600951</v>
+        <v>2.525751013515455</v>
       </c>
       <c r="E8" t="n">
-        <v>16.06448901065523</v>
+        <v>2.610479464231475</v>
       </c>
       <c r="F8" t="n">
-        <v>16.01887623980861</v>
+        <v>2.6030673889689</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>37.92427106491261</v>
+        <v>6.1626940480483</v>
       </c>
       <c r="D9" t="n">
-        <v>17.17051763487062</v>
+        <v>2.790209115666476</v>
       </c>
       <c r="E9" t="n">
-        <v>16.06448901065523</v>
+        <v>2.610479464231475</v>
       </c>
       <c r="F9" t="n">
-        <v>16.01887623980861</v>
+        <v>2.6030673889689</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>29.81968479097333</v>
+        <v>4.845698778533166</v>
       </c>
       <c r="D10" t="n">
-        <v>29.7047325293119</v>
+        <v>4.827019036013184</v>
       </c>
       <c r="E10" t="n">
-        <v>16.06448901065523</v>
+        <v>2.610479464231475</v>
       </c>
       <c r="F10" t="n">
-        <v>16.01887623980861</v>
+        <v>2.6030673889689</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>33.10094237766855</v>
+        <v>5.378903136371139</v>
       </c>
       <c r="D11" t="n">
-        <v>31.06010339316072</v>
+        <v>5.047266801388616</v>
       </c>
       <c r="E11" t="n">
-        <v>16.06448901065523</v>
+        <v>2.610479464231475</v>
       </c>
       <c r="F11" t="n">
-        <v>16.01887623980861</v>
+        <v>2.6030673889689</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>18.58505516903785</v>
+        <v>3.02007146496865</v>
       </c>
       <c r="D12" t="n">
-        <v>18.86766810103828</v>
+        <v>3.065996066418721</v>
       </c>
       <c r="E12" t="n">
-        <v>16.06448901065523</v>
+        <v>2.610479464231475</v>
       </c>
       <c r="F12" t="n">
-        <v>16.01887623980861</v>
+        <v>2.6030673889689</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>43.9768108758019</v>
+        <v>7.14623176731781</v>
       </c>
       <c r="D13" t="n">
-        <v>31.02135168922704</v>
+        <v>5.040969649499393</v>
       </c>
       <c r="E13" t="n">
-        <v>16.06448901065523</v>
+        <v>2.610479464231475</v>
       </c>
       <c r="F13" t="n">
-        <v>16.01887623980861</v>
+        <v>2.6030673889689</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>21.95179158491471</v>
+        <v>3.567166132548641</v>
       </c>
       <c r="D14" t="n">
-        <v>24.59895711872827</v>
+        <v>3.997330531793344</v>
       </c>
       <c r="E14" t="n">
-        <v>16.06448901065523</v>
+        <v>2.610479464231475</v>
       </c>
       <c r="F14" t="n">
-        <v>16.01887623980861</v>
+        <v>2.6030673889689</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>13</v>
+        <v>2.1125</v>
       </c>
       <c r="D15" t="n">
-        <v>6.353991790650904</v>
+        <v>1.032523665980772</v>
       </c>
       <c r="E15" t="n">
-        <v>16.06448901065523</v>
+        <v>2.610479464231475</v>
       </c>
       <c r="F15" t="n">
-        <v>16.01887623980861</v>
+        <v>2.6030673889689</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>2.906966274039254</v>
+        <v>0.4723820195313788</v>
       </c>
       <c r="D16" t="n">
-        <v>2.906966274039254</v>
+        <v>0.4723820195313788</v>
       </c>
       <c r="E16" t="n">
-        <v>16.06448901065523</v>
+        <v>2.610479464231475</v>
       </c>
       <c r="F16" t="n">
-        <v>16.01887623980861</v>
+        <v>2.6030673889689</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>14.36273095762223</v>
+        <v>2.333943780613613</v>
       </c>
       <c r="D17" t="n">
-        <v>9.76707473192571</v>
+        <v>1.587149643937928</v>
       </c>
       <c r="E17" t="n">
-        <v>16.06448901065523</v>
+        <v>2.610479464231475</v>
       </c>
       <c r="F17" t="n">
-        <v>16.01887623980861</v>
+        <v>2.6030673889689</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
